--- a/artfynd/A 4264-2024 artfynd.xlsx
+++ b/artfynd/A 4264-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4264-2024 artfynd.xlsx
+++ b/artfynd/A 4264-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88922</v>
+        <v>88904</v>
       </c>
       <c r="B2" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591242.8472568495</v>
+        <v>591368</v>
       </c>
       <c r="R2" t="n">
-        <v>6665123.637964937</v>
+        <v>6665156</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2007-07-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2007-11-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88910</v>
+        <v>88905</v>
       </c>
       <c r="B3" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591190.5952173112</v>
+        <v>591360</v>
       </c>
       <c r="R3" t="n">
-        <v>6665035.062865729</v>
+        <v>6665094</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2007-07-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2007-11-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>279921</v>
+        <v>88908</v>
       </c>
       <c r="B4" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591243.6437227748</v>
+        <v>591349</v>
       </c>
       <c r="R4" t="n">
-        <v>6665111.688430686</v>
+        <v>6665113</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +945,9 @@
           <t>2007-07-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2007-11-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88904</v>
+        <v>88910</v>
       </c>
       <c r="B5" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591368.4251340069</v>
+        <v>591191</v>
       </c>
       <c r="R5" t="n">
-        <v>6665156.184790905</v>
+        <v>6665035</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,19 +1046,9 @@
           <t>2007-07-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2007-11-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>88921</v>
+        <v>88918</v>
       </c>
       <c r="B6" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591327.6201264029</v>
+        <v>591371</v>
       </c>
       <c r="R6" t="n">
-        <v>6665129.735056195</v>
+        <v>6665208</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,19 +1147,9 @@
           <t>2007-07-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2007-11-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,50 +1180,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4886526</v>
+        <v>88919</v>
       </c>
       <c r="B7" t="n">
-        <v>101323</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222395</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Acksjön, Björsbo, Vstm</t>
+          <t>Acksjön, Björsbo (delomr 11), Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591313.9386683218</v>
+        <v>591335</v>
       </c>
       <c r="R7" t="n">
-        <v>6665117.425504647</v>
+        <v>6665198</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1328,19 +1248,9 @@
           <t>2007-07-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2007-11-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>88919</v>
+        <v>88920</v>
       </c>
       <c r="B8" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591334.9206164561</v>
+        <v>591279</v>
       </c>
       <c r="R8" t="n">
-        <v>6665197.742045668</v>
+        <v>6665198</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1444,19 +1349,9 @@
           <t>2007-07-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2007-11-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>88918</v>
+        <v>88921</v>
       </c>
       <c r="B9" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591370.6300769587</v>
+        <v>591328</v>
       </c>
       <c r="R9" t="n">
-        <v>6665208.105921667</v>
+        <v>6665130</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1560,19 +1450,9 @@
           <t>2007-07-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2007-11-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>88908</v>
+        <v>88922</v>
       </c>
       <c r="B10" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591349.0224276494</v>
+        <v>591243</v>
       </c>
       <c r="R10" t="n">
-        <v>6665112.81211972</v>
+        <v>6665124</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1676,19 +1551,9 @@
           <t>2007-07-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2007-11-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,12 +1587,7 @@
         <v>88926</v>
       </c>
       <c r="B11" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1759,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591391.9080966513</v>
+        <v>591392</v>
       </c>
       <c r="R11" t="n">
-        <v>6665196.167643974</v>
+        <v>6665196</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1792,19 +1652,9 @@
           <t>2007-07-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2007-11-30</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,15 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>88905</v>
+        <v>279921</v>
       </c>
       <c r="B12" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1851,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1875,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591359.9778503045</v>
+        <v>591244</v>
       </c>
       <c r="R12" t="n">
-        <v>6665094.133123328</v>
+        <v>6665112</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1908,19 +1753,9 @@
           <t>2007-07-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2007-11-30</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,6 +1779,107 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>4886526</v>
+      </c>
+      <c r="B13" t="n">
+        <v>104253</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222395</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dvärghäxört</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Circaea alpina</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Acksjön, Björsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>591314</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6665117</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2007-07-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2007-11-30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
         <is>
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>

--- a/artfynd/A 4264-2024 artfynd.xlsx
+++ b/artfynd/A 4264-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88904</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88905</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88908</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88910</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88918</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88919</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88920</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88921</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88922</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88926</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/279921</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,8 +1944,27 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4886526</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>